--- a/Spanish Adjectives.xlsx
+++ b/Spanish Adjectives.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="667">
   <si>
     <t>prononciation</t>
   </si>
@@ -1363,6 +1363,660 @@
   </si>
   <si>
     <t>duro / a</t>
+  </si>
+  <si>
+    <t>rojo / a</t>
+  </si>
+  <si>
+    <t>paciente</t>
+  </si>
+  <si>
+    <t>patient</t>
+  </si>
+  <si>
+    <t>peligroso / a</t>
+  </si>
+  <si>
+    <t>dangerous</t>
+  </si>
+  <si>
+    <t>perfecto / a</t>
+  </si>
+  <si>
+    <t>perfect</t>
+  </si>
+  <si>
+    <t>amplio / a</t>
+  </si>
+  <si>
+    <t>spacious</t>
+  </si>
+  <si>
+    <t>animado / a</t>
+  </si>
+  <si>
+    <t>lively</t>
+  </si>
+  <si>
+    <t>poderoso / a</t>
+  </si>
+  <si>
+    <t>powerful</t>
+  </si>
+  <si>
+    <t>popular</t>
+  </si>
+  <si>
+    <t>apasionado / a</t>
+  </si>
+  <si>
+    <t>passionate</t>
+  </si>
+  <si>
+    <t>positivo / a</t>
+  </si>
+  <si>
+    <t>positive</t>
+  </si>
+  <si>
+    <t>apropiado / a</t>
+  </si>
+  <si>
+    <t>appropriate</t>
+  </si>
+  <si>
+    <t>práctico / a</t>
+  </si>
+  <si>
+    <t>practical</t>
+  </si>
+  <si>
+    <t>atractivo / a</t>
+  </si>
+  <si>
+    <t>attractive</t>
+  </si>
+  <si>
+    <t>precioso / a</t>
+  </si>
+  <si>
+    <t>precious</t>
+  </si>
+  <si>
+    <t>atrevido / a</t>
+  </si>
+  <si>
+    <t>bold</t>
+  </si>
+  <si>
+    <t>precavido / a</t>
+  </si>
+  <si>
+    <t>cautious</t>
+  </si>
+  <si>
+    <t>principal</t>
+  </si>
+  <si>
+    <t>main</t>
+  </si>
+  <si>
+    <t>profesional</t>
+  </si>
+  <si>
+    <t>professional</t>
+  </si>
+  <si>
+    <t>profundo / a</t>
+  </si>
+  <si>
+    <t>deep</t>
+  </si>
+  <si>
+    <t>bueno / a</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>puro / a</t>
+  </si>
+  <si>
+    <t>pure</t>
+  </si>
+  <si>
+    <t>brillante</t>
+  </si>
+  <si>
+    <t>brilliant</t>
+  </si>
+  <si>
+    <t>real</t>
+  </si>
+  <si>
+    <t>red</t>
+  </si>
+  <si>
+    <t>cuidadoso / a</t>
+  </si>
+  <si>
+    <t>careful</t>
+  </si>
+  <si>
+    <t>romántico / a</t>
+  </si>
+  <si>
+    <t>romantic</t>
+  </si>
+  <si>
+    <t>raro / a</t>
+  </si>
+  <si>
+    <t>rare/strange</t>
+  </si>
+  <si>
+    <t>salvaje</t>
+  </si>
+  <si>
+    <t>wild</t>
+  </si>
+  <si>
+    <t>curioso / a</t>
+  </si>
+  <si>
+    <t>curious</t>
+  </si>
+  <si>
+    <t>satisfecho / a</t>
+  </si>
+  <si>
+    <t>satisfied</t>
+  </si>
+  <si>
+    <t>secreto / a</t>
+  </si>
+  <si>
+    <t>secret</t>
+  </si>
+  <si>
+    <t>completo / a</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>serio / a</t>
+  </si>
+  <si>
+    <t>serious</t>
+  </si>
+  <si>
+    <t>correcto / a</t>
+  </si>
+  <si>
+    <t>correct</t>
+  </si>
+  <si>
+    <t>creativo / a</t>
+  </si>
+  <si>
+    <t>creative</t>
+  </si>
+  <si>
+    <t>delicado / a</t>
+  </si>
+  <si>
+    <t>delicate</t>
+  </si>
+  <si>
+    <t>tibio / a</t>
+  </si>
+  <si>
+    <t>lukewarm</t>
+  </si>
+  <si>
+    <t>torcido / a</t>
+  </si>
+  <si>
+    <t>crooked</t>
+  </si>
+  <si>
+    <t>útil</t>
+  </si>
+  <si>
+    <t>useful</t>
+  </si>
+  <si>
+    <t>enojado / a</t>
+  </si>
+  <si>
+    <t>enamorado / a</t>
+  </si>
+  <si>
+    <t>in love</t>
+  </si>
+  <si>
+    <t>enérgico / a</t>
+  </si>
+  <si>
+    <t>energetic</t>
+  </si>
+  <si>
+    <t>viejo / a</t>
+  </si>
+  <si>
+    <t>old</t>
+  </si>
+  <si>
+    <t>enorme</t>
+  </si>
+  <si>
+    <t>huge</t>
+  </si>
+  <si>
+    <t>verde</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>equivocado / a</t>
+  </si>
+  <si>
+    <t>wrong</t>
+  </si>
+  <si>
+    <t>visible</t>
+  </si>
+  <si>
+    <t>vulgar</t>
+  </si>
+  <si>
+    <t>falso / a</t>
+  </si>
+  <si>
+    <t>amarillo / a</t>
+  </si>
+  <si>
+    <t>yellow</t>
+  </si>
+  <si>
+    <t>famoso / a</t>
+  </si>
+  <si>
+    <t>famous</t>
+  </si>
+  <si>
+    <t>azul</t>
+  </si>
+  <si>
+    <t>blue</t>
+  </si>
+  <si>
+    <t>blanco / a</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>negro / a</t>
+  </si>
+  <si>
+    <t>black</t>
+  </si>
+  <si>
+    <t>naranja</t>
+  </si>
+  <si>
+    <t>orange</t>
+  </si>
+  <si>
+    <t>rosa</t>
+  </si>
+  <si>
+    <t>pink</t>
+  </si>
+  <si>
+    <t>marrón</t>
+  </si>
+  <si>
+    <t>brown</t>
+  </si>
+  <si>
+    <t>dorado / a</t>
+  </si>
+  <si>
+    <t>golden</t>
+  </si>
+  <si>
+    <t>plateado / a</t>
+  </si>
+  <si>
+    <t>silver</t>
+  </si>
+  <si>
+    <t>gracioso / a</t>
+  </si>
+  <si>
+    <t>funny</t>
+  </si>
+  <si>
+    <t>púrpura</t>
+  </si>
+  <si>
+    <t>purple</t>
+  </si>
+  <si>
+    <t>violeta</t>
+  </si>
+  <si>
+    <t>violet</t>
+  </si>
+  <si>
+    <t>gris</t>
+  </si>
+  <si>
+    <t>gray</t>
+  </si>
+  <si>
+    <t>grosero / a</t>
+  </si>
+  <si>
+    <t>fiel</t>
+  </si>
+  <si>
+    <t>loyal</t>
+  </si>
+  <si>
+    <t>grueso / a</t>
+  </si>
+  <si>
+    <t>thick</t>
+  </si>
+  <si>
+    <t>leal</t>
+  </si>
+  <si>
+    <t>humilde</t>
+  </si>
+  <si>
+    <t>humble</t>
+  </si>
+  <si>
+    <t>sabio / a</t>
+  </si>
+  <si>
+    <t>wise</t>
+  </si>
+  <si>
+    <t>importante</t>
+  </si>
+  <si>
+    <t>important</t>
+  </si>
+  <si>
+    <t>callado / a</t>
+  </si>
+  <si>
+    <t>imposible</t>
+  </si>
+  <si>
+    <t>impossible</t>
+  </si>
+  <si>
+    <t>hablador / a</t>
+  </si>
+  <si>
+    <t>talkative</t>
+  </si>
+  <si>
+    <t>increíble</t>
+  </si>
+  <si>
+    <t>incredible</t>
+  </si>
+  <si>
+    <t>miedoso / a</t>
+  </si>
+  <si>
+    <t>celoso / a</t>
+  </si>
+  <si>
+    <t>jealous</t>
+  </si>
+  <si>
+    <t>envidioso / a</t>
+  </si>
+  <si>
+    <t>envious</t>
+  </si>
+  <si>
+    <t>intenso / a</t>
+  </si>
+  <si>
+    <t>intense</t>
+  </si>
+  <si>
+    <t>agradecido / a</t>
+  </si>
+  <si>
+    <t>grateful</t>
+  </si>
+  <si>
+    <t>inútil</t>
+  </si>
+  <si>
+    <t>useless</t>
+  </si>
+  <si>
+    <t>decepcionado / a</t>
+  </si>
+  <si>
+    <t>disappointed</t>
+  </si>
+  <si>
+    <t>interesado / a</t>
+  </si>
+  <si>
+    <t>interested</t>
+  </si>
+  <si>
+    <t>joven</t>
+  </si>
+  <si>
+    <t>young</t>
+  </si>
+  <si>
+    <t>cansado / a</t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t>loco / a</t>
+  </si>
+  <si>
+    <t>crazy</t>
+  </si>
+  <si>
+    <t>avergonzado / a</t>
+  </si>
+  <si>
+    <t>embarrassed</t>
+  </si>
+  <si>
+    <t>luminoso / a</t>
+  </si>
+  <si>
+    <t>luminous</t>
+  </si>
+  <si>
+    <t>ofendido / a</t>
+  </si>
+  <si>
+    <t>offended</t>
+  </si>
+  <si>
+    <t>magnífico / a</t>
+  </si>
+  <si>
+    <t>magnificent</t>
+  </si>
+  <si>
+    <t>malo / a</t>
+  </si>
+  <si>
+    <t>bad</t>
+  </si>
+  <si>
+    <t>fastidioso / a</t>
+  </si>
+  <si>
+    <t>tedious</t>
+  </si>
+  <si>
+    <t>mayor</t>
+  </si>
+  <si>
+    <t>older/greater</t>
+  </si>
+  <si>
+    <t>monótono / a</t>
+  </si>
+  <si>
+    <t>monotonous</t>
+  </si>
+  <si>
+    <t>menor</t>
+  </si>
+  <si>
+    <t>younger/less</t>
+  </si>
+  <si>
+    <t>predecible</t>
+  </si>
+  <si>
+    <t>predictable</t>
+  </si>
+  <si>
+    <t>sorprendente</t>
+  </si>
+  <si>
+    <t>surprising</t>
+  </si>
+  <si>
+    <t>misterioso / a</t>
+  </si>
+  <si>
+    <t>mysterious</t>
+  </si>
+  <si>
+    <t>asombroso / a</t>
+  </si>
+  <si>
+    <t>amazing</t>
+  </si>
+  <si>
+    <t>mágico / a</t>
+  </si>
+  <si>
+    <t>magical</t>
+  </si>
+  <si>
+    <t>extraordinario / a</t>
+  </si>
+  <si>
+    <t>extraordinary</t>
+  </si>
+  <si>
+    <t>natural</t>
+  </si>
+  <si>
+    <t>sobresaliente</t>
+  </si>
+  <si>
+    <t>outstanding</t>
+  </si>
+  <si>
+    <t>notable</t>
+  </si>
+  <si>
+    <t>nuevo / a</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>significativo / a</t>
+  </si>
+  <si>
+    <t>significant</t>
+  </si>
+  <si>
+    <t>noble</t>
+  </si>
+  <si>
+    <t>esencial</t>
+  </si>
+  <si>
+    <t>essential</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>fundamental</t>
+  </si>
+  <si>
+    <t>obeso / a</t>
+  </si>
+  <si>
+    <t>obese</t>
+  </si>
+  <si>
+    <t>crucial</t>
+  </si>
+  <si>
+    <t>ocupado / a</t>
+  </si>
+  <si>
+    <t>busy</t>
+  </si>
+  <si>
+    <t>decisivo / a</t>
+  </si>
+  <si>
+    <t>decisive</t>
+  </si>
+  <si>
+    <t>ordenado / a</t>
+  </si>
+  <si>
+    <t>neat</t>
+  </si>
+  <si>
+    <t>original</t>
+  </si>
+  <si>
+    <t>justo / a</t>
+  </si>
+  <si>
+    <t>fair</t>
+  </si>
+  <si>
+    <t>listo / a</t>
+  </si>
+  <si>
+    <t>ready/smart</t>
+  </si>
+  <si>
+    <t>honesto / a</t>
+  </si>
+  <si>
+    <t>honest</t>
+  </si>
+  <si>
+    <t>false</t>
   </si>
 </sst>
 </file>
@@ -1398,13 +2052,134 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1732,9 +2507,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D227"/>
+  <dimension ref="B1:D345"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="2.5703125" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" customWidth="1"/>
     <col min="4" max="4" width="59.85546875" bestFit="1" customWidth="1"/>
@@ -4237,15 +5013,1322 @@
         <v>279</v>
       </c>
     </row>
+    <row r="228" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B228" t="s">
+        <v>456</v>
+      </c>
+      <c r="C228" t="s">
+        <v>456</v>
+      </c>
+      <c r="D228" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B229" t="s">
+        <v>458</v>
+      </c>
+      <c r="C229" t="s">
+        <v>458</v>
+      </c>
+      <c r="D229" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B230" t="s">
+        <v>463</v>
+      </c>
+      <c r="C230" t="s">
+        <v>463</v>
+      </c>
+      <c r="D230" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B231" t="s">
+        <v>467</v>
+      </c>
+      <c r="C231" t="s">
+        <v>467</v>
+      </c>
+      <c r="D231" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B232" t="s">
+        <v>471</v>
+      </c>
+      <c r="C232" t="s">
+        <v>471</v>
+      </c>
+      <c r="D232" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B233" t="s">
+        <v>475</v>
+      </c>
+      <c r="C233" t="s">
+        <v>475</v>
+      </c>
+      <c r="D233" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B234" t="s">
+        <v>489</v>
+      </c>
+      <c r="C234" t="s">
+        <v>489</v>
+      </c>
+      <c r="D234" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="235" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B235" t="s">
+        <v>493</v>
+      </c>
+      <c r="C235" t="s">
+        <v>493</v>
+      </c>
+      <c r="D235" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B236" t="s">
+        <v>501</v>
+      </c>
+      <c r="C236" t="s">
+        <v>501</v>
+      </c>
+      <c r="D236" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B237" t="s">
+        <v>507</v>
+      </c>
+      <c r="C237" t="s">
+        <v>507</v>
+      </c>
+      <c r="D237" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="238" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B238" t="s">
+        <v>511</v>
+      </c>
+      <c r="C238" t="s">
+        <v>511</v>
+      </c>
+      <c r="D238" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B239" t="s">
+        <v>513</v>
+      </c>
+      <c r="C239" t="s">
+        <v>513</v>
+      </c>
+      <c r="D239" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="240" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B240" t="s">
+        <v>515</v>
+      </c>
+      <c r="C240" t="s">
+        <v>515</v>
+      </c>
+      <c r="D240" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="241" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B241" t="s">
+        <v>523</v>
+      </c>
+      <c r="C241" t="s">
+        <v>523</v>
+      </c>
+      <c r="D241" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="242" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B242" t="s">
+        <v>524</v>
+      </c>
+      <c r="C242" t="s">
+        <v>524</v>
+      </c>
+      <c r="D242" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="243" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B243" t="s">
+        <v>526</v>
+      </c>
+      <c r="C243" t="s">
+        <v>526</v>
+      </c>
+      <c r="D243" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="244" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B244" t="s">
+        <v>530</v>
+      </c>
+      <c r="C244" t="s">
+        <v>530</v>
+      </c>
+      <c r="D244" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="245" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B245" t="s">
+        <v>534</v>
+      </c>
+      <c r="C245" t="s">
+        <v>534</v>
+      </c>
+      <c r="D245" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="246" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B246" t="s">
+        <v>538</v>
+      </c>
+      <c r="C246" t="s">
+        <v>538</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="247" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B247" t="s">
+        <v>541</v>
+      </c>
+      <c r="C247" t="s">
+        <v>541</v>
+      </c>
+      <c r="D247" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="248" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B248" t="s">
+        <v>559</v>
+      </c>
+      <c r="C248" t="s">
+        <v>559</v>
+      </c>
+      <c r="D248" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="249" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B249" t="s">
+        <v>565</v>
+      </c>
+      <c r="C249" t="s">
+        <v>565</v>
+      </c>
+      <c r="D249" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="250" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B250" t="s">
+        <v>567</v>
+      </c>
+      <c r="C250" t="s">
+        <v>567</v>
+      </c>
+      <c r="D250" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="251" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B251" t="s">
+        <v>570</v>
+      </c>
+      <c r="C251" t="s">
+        <v>570</v>
+      </c>
+      <c r="D251" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="252" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B252" t="s">
+        <v>577</v>
+      </c>
+      <c r="C252" t="s">
+        <v>577</v>
+      </c>
+      <c r="D252" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="253" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B253" t="s">
+        <v>580</v>
+      </c>
+      <c r="C253" t="s">
+        <v>580</v>
+      </c>
+      <c r="D253" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="254" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B254" t="s">
+        <v>584</v>
+      </c>
+      <c r="C254" t="s">
+        <v>584</v>
+      </c>
+      <c r="D254" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="255" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B255" t="s">
+        <v>591</v>
+      </c>
+      <c r="C255" t="s">
+        <v>591</v>
+      </c>
+      <c r="D255" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="256" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B256" t="s">
+        <v>595</v>
+      </c>
+      <c r="C256" t="s">
+        <v>595</v>
+      </c>
+      <c r="D256" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="257" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B257" t="s">
+        <v>599</v>
+      </c>
+      <c r="C257" t="s">
+        <v>599</v>
+      </c>
+      <c r="D257" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="258" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B258" t="s">
+        <v>601</v>
+      </c>
+      <c r="C258" t="s">
+        <v>601</v>
+      </c>
+      <c r="D258" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="259" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B259" t="s">
+        <v>605</v>
+      </c>
+      <c r="C259" t="s">
+        <v>605</v>
+      </c>
+      <c r="D259" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="260" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B260" t="s">
+        <v>609</v>
+      </c>
+      <c r="C260" t="s">
+        <v>609</v>
+      </c>
+      <c r="D260" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="261" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B261" t="s">
+        <v>613</v>
+      </c>
+      <c r="C261" t="s">
+        <v>613</v>
+      </c>
+      <c r="D261" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="262" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B262" t="s">
+        <v>619</v>
+      </c>
+      <c r="C262" t="s">
+        <v>619</v>
+      </c>
+      <c r="D262" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="263" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B263" t="s">
+        <v>623</v>
+      </c>
+      <c r="C263" t="s">
+        <v>623</v>
+      </c>
+      <c r="D263" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="264" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B264" t="s">
+        <v>629</v>
+      </c>
+      <c r="C264" t="s">
+        <v>629</v>
+      </c>
+      <c r="D264" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="265" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B265" t="s">
+        <v>633</v>
+      </c>
+      <c r="C265" t="s">
+        <v>633</v>
+      </c>
+      <c r="D265" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="266" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B266" t="s">
+        <v>637</v>
+      </c>
+      <c r="C266" t="s">
+        <v>637</v>
+      </c>
+      <c r="D266" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="267" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B267" t="s">
+        <v>641</v>
+      </c>
+      <c r="C267" t="s">
+        <v>641</v>
+      </c>
+      <c r="D267" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="268" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B268" t="s">
+        <v>645</v>
+      </c>
+      <c r="C268" t="s">
+        <v>645</v>
+      </c>
+      <c r="D268" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="269" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B269" t="s">
+        <v>648</v>
+      </c>
+      <c r="C269" t="s">
+        <v>648</v>
+      </c>
+      <c r="D269" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="270" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B270" t="s">
+        <v>650</v>
+      </c>
+      <c r="C270" t="s">
+        <v>650</v>
+      </c>
+      <c r="D270" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="271" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B271" t="s">
+        <v>653</v>
+      </c>
+      <c r="C271" t="s">
+        <v>653</v>
+      </c>
+      <c r="D271" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="272" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B272" t="s">
+        <v>657</v>
+      </c>
+      <c r="C272" t="s">
+        <v>657</v>
+      </c>
+      <c r="D272" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="273" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B273" t="s">
+        <v>659</v>
+      </c>
+      <c r="C273" t="s">
+        <v>659</v>
+      </c>
+      <c r="D273" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="274" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B274" t="s">
+        <v>662</v>
+      </c>
+      <c r="C274" t="s">
+        <v>662</v>
+      </c>
+      <c r="D274" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="275" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B275" t="s">
+        <v>450</v>
+      </c>
+      <c r="C275" t="s">
+        <v>450</v>
+      </c>
+      <c r="D275" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="276" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B276" t="s">
+        <v>452</v>
+      </c>
+      <c r="C276" t="s">
+        <v>452</v>
+      </c>
+      <c r="D276" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="277" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B277" t="s">
+        <v>454</v>
+      </c>
+      <c r="C277" t="s">
+        <v>454</v>
+      </c>
+      <c r="D277" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="278" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B278" t="s">
+        <v>460</v>
+      </c>
+      <c r="C278" t="s">
+        <v>460</v>
+      </c>
+      <c r="D278" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="279" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B279" t="s">
+        <v>462</v>
+      </c>
+      <c r="C279" t="s">
+        <v>462</v>
+      </c>
+      <c r="D279" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="280" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B280" t="s">
+        <v>465</v>
+      </c>
+      <c r="C280" t="s">
+        <v>465</v>
+      </c>
+      <c r="D280" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="281" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B281" t="s">
+        <v>469</v>
+      </c>
+      <c r="C281" t="s">
+        <v>469</v>
+      </c>
+      <c r="D281" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="282" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B282" t="s">
+        <v>473</v>
+      </c>
+      <c r="C282" t="s">
+        <v>473</v>
+      </c>
+      <c r="D282" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="283" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B283" t="s">
+        <v>477</v>
+      </c>
+      <c r="C283" t="s">
+        <v>477</v>
+      </c>
+      <c r="D283" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="284" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B284" t="s">
+        <v>479</v>
+      </c>
+      <c r="C284" t="s">
+        <v>479</v>
+      </c>
+      <c r="D284" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="285" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B285" t="s">
+        <v>481</v>
+      </c>
+      <c r="C285" t="s">
+        <v>481</v>
+      </c>
+      <c r="D285" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="286" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B286" t="s">
+        <v>483</v>
+      </c>
+      <c r="C286" t="s">
+        <v>483</v>
+      </c>
+      <c r="D286" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="287" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B287" t="s">
+        <v>487</v>
+      </c>
+      <c r="C287" t="s">
+        <v>487</v>
+      </c>
+      <c r="D287" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="288" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B288" t="s">
+        <v>491</v>
+      </c>
+      <c r="C288" t="s">
+        <v>491</v>
+      </c>
+      <c r="D288" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="289" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B289" t="s">
+        <v>449</v>
+      </c>
+      <c r="C289" t="s">
+        <v>449</v>
+      </c>
+      <c r="D289" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="290" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B290" t="s">
+        <v>495</v>
+      </c>
+      <c r="C290" t="s">
+        <v>495</v>
+      </c>
+      <c r="D290" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="291" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B291" t="s">
+        <v>497</v>
+      </c>
+      <c r="C291" t="s">
+        <v>497</v>
+      </c>
+      <c r="D291" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="292" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B292" t="s">
+        <v>499</v>
+      </c>
+      <c r="C292" t="s">
+        <v>499</v>
+      </c>
+      <c r="D292" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="293" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B293" t="s">
+        <v>503</v>
+      </c>
+      <c r="C293" t="s">
+        <v>503</v>
+      </c>
+      <c r="D293" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="294" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B294" t="s">
+        <v>505</v>
+      </c>
+      <c r="C294" t="s">
+        <v>505</v>
+      </c>
+      <c r="D294" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="295" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B295" t="s">
+        <v>509</v>
+      </c>
+      <c r="C295" t="s">
+        <v>509</v>
+      </c>
+      <c r="D295" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="296" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B296" t="s">
+        <v>258</v>
+      </c>
+      <c r="C296" t="s">
+        <v>258</v>
+      </c>
+      <c r="D296" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="297" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B297" t="s">
+        <v>517</v>
+      </c>
+      <c r="C297" t="s">
+        <v>517</v>
+      </c>
+      <c r="D297" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="298" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B298" t="s">
+        <v>519</v>
+      </c>
+      <c r="C298" t="s">
+        <v>519</v>
+      </c>
+      <c r="D298" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="299" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B299" t="s">
+        <v>521</v>
+      </c>
+      <c r="C299" t="s">
+        <v>521</v>
+      </c>
+      <c r="D299" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="300" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B300" t="s">
+        <v>528</v>
+      </c>
+      <c r="C300" t="s">
+        <v>528</v>
+      </c>
+      <c r="D300" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="301" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B301" t="s">
+        <v>532</v>
+      </c>
+      <c r="C301" t="s">
+        <v>532</v>
+      </c>
+      <c r="D301" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="302" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B302" t="s">
+        <v>536</v>
+      </c>
+      <c r="C302" t="s">
+        <v>536</v>
+      </c>
+      <c r="D302" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="303" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B303" t="s">
+        <v>537</v>
+      </c>
+      <c r="C303" t="s">
+        <v>537</v>
+      </c>
+      <c r="D303" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="304" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B304" t="s">
+        <v>539</v>
+      </c>
+      <c r="C304" t="s">
+        <v>539</v>
+      </c>
+      <c r="D304" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="305" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B305" t="s">
+        <v>543</v>
+      </c>
+      <c r="C305" t="s">
+        <v>543</v>
+      </c>
+      <c r="D305" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="306" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B306" t="s">
+        <v>545</v>
+      </c>
+      <c r="C306" t="s">
+        <v>545</v>
+      </c>
+      <c r="D306" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="307" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B307" t="s">
+        <v>547</v>
+      </c>
+      <c r="C307" t="s">
+        <v>547</v>
+      </c>
+      <c r="D307" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="308" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B308" t="s">
+        <v>549</v>
+      </c>
+      <c r="C308" t="s">
+        <v>549</v>
+      </c>
+      <c r="D308" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="309" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B309" t="s">
+        <v>551</v>
+      </c>
+      <c r="C309" t="s">
+        <v>551</v>
+      </c>
+      <c r="D309" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="310" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B310" t="s">
+        <v>553</v>
+      </c>
+      <c r="C310" t="s">
+        <v>553</v>
+      </c>
+      <c r="D310" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="311" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B311" t="s">
+        <v>555</v>
+      </c>
+      <c r="C311" t="s">
+        <v>555</v>
+      </c>
+      <c r="D311" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="312" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B312" t="s">
+        <v>557</v>
+      </c>
+      <c r="C312" t="s">
+        <v>557</v>
+      </c>
+      <c r="D312" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="313" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B313" t="s">
+        <v>561</v>
+      </c>
+      <c r="C313" t="s">
+        <v>561</v>
+      </c>
+      <c r="D313" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="314" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B314" t="s">
+        <v>563</v>
+      </c>
+      <c r="C314" t="s">
+        <v>563</v>
+      </c>
+      <c r="D314" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="315" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B315" t="s">
+        <v>573</v>
+      </c>
+      <c r="C315" t="s">
+        <v>573</v>
+      </c>
+      <c r="D315" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="316" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B316" t="s">
+        <v>575</v>
+      </c>
+      <c r="C316" t="s">
+        <v>575</v>
+      </c>
+      <c r="D316" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="317" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B317" t="s">
+        <v>579</v>
+      </c>
+      <c r="C317" t="s">
+        <v>579</v>
+      </c>
+      <c r="D317" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="318" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B318" t="s">
+        <v>582</v>
+      </c>
+      <c r="C318" t="s">
+        <v>582</v>
+      </c>
+      <c r="D318" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="319" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B319" t="s">
+        <v>586</v>
+      </c>
+      <c r="C319" t="s">
+        <v>586</v>
+      </c>
+      <c r="D319" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="320" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B320" t="s">
+        <v>587</v>
+      </c>
+      <c r="C320" t="s">
+        <v>587</v>
+      </c>
+      <c r="D320" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="321" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B321" t="s">
+        <v>589</v>
+      </c>
+      <c r="C321" t="s">
+        <v>589</v>
+      </c>
+      <c r="D321" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="322" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B322" t="s">
+        <v>593</v>
+      </c>
+      <c r="C322" t="s">
+        <v>593</v>
+      </c>
+      <c r="D322" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="323" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B323" t="s">
+        <v>597</v>
+      </c>
+      <c r="C323" t="s">
+        <v>597</v>
+      </c>
+      <c r="D323" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="324" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B324" t="s">
+        <v>603</v>
+      </c>
+      <c r="C324" t="s">
+        <v>603</v>
+      </c>
+      <c r="D324" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="325" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B325" t="s">
+        <v>607</v>
+      </c>
+      <c r="C325" t="s">
+        <v>607</v>
+      </c>
+      <c r="D325" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="326" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B326" t="s">
+        <v>611</v>
+      </c>
+      <c r="C326" t="s">
+        <v>611</v>
+      </c>
+      <c r="D326" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="327" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B327" t="s">
+        <v>617</v>
+      </c>
+      <c r="C327" t="s">
+        <v>617</v>
+      </c>
+      <c r="D327" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="328" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B328" t="s">
+        <v>621</v>
+      </c>
+      <c r="C328" t="s">
+        <v>621</v>
+      </c>
+      <c r="D328" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="329" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B329" t="s">
+        <v>625</v>
+      </c>
+      <c r="C329" t="s">
+        <v>625</v>
+      </c>
+      <c r="D329" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="330" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B330" t="s">
+        <v>627</v>
+      </c>
+      <c r="C330" t="s">
+        <v>627</v>
+      </c>
+      <c r="D330" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="331" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B331" t="s">
+        <v>631</v>
+      </c>
+      <c r="C331" t="s">
+        <v>631</v>
+      </c>
+      <c r="D331" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="332" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B332" t="s">
+        <v>635</v>
+      </c>
+      <c r="C332" t="s">
+        <v>635</v>
+      </c>
+      <c r="D332" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="333" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B333" t="s">
+        <v>638</v>
+      </c>
+      <c r="C333" t="s">
+        <v>638</v>
+      </c>
+      <c r="D333" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="334" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B334" t="s">
+        <v>640</v>
+      </c>
+      <c r="C334" t="s">
+        <v>640</v>
+      </c>
+      <c r="D334" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="335" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B335" t="s">
+        <v>643</v>
+      </c>
+      <c r="C335" t="s">
+        <v>643</v>
+      </c>
+      <c r="D335" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="336" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B336" t="s">
+        <v>646</v>
+      </c>
+      <c r="C336" t="s">
+        <v>646</v>
+      </c>
+      <c r="D336" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="337" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B337" t="s">
+        <v>649</v>
+      </c>
+      <c r="C337" t="s">
+        <v>649</v>
+      </c>
+      <c r="D337" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="338" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B338" t="s">
+        <v>652</v>
+      </c>
+      <c r="C338" t="s">
+        <v>652</v>
+      </c>
+      <c r="D338" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="339" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B339" t="s">
+        <v>655</v>
+      </c>
+      <c r="C339" t="s">
+        <v>655</v>
+      </c>
+      <c r="D339" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="340" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B340" t="s">
+        <v>615</v>
+      </c>
+      <c r="C340" t="s">
+        <v>615</v>
+      </c>
+      <c r="D340" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="341" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B341" t="s">
+        <v>485</v>
+      </c>
+      <c r="C341" t="s">
+        <v>485</v>
+      </c>
+      <c r="D341" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="342" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B342" t="s">
+        <v>660</v>
+      </c>
+      <c r="C342" t="s">
+        <v>660</v>
+      </c>
+      <c r="D342" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="343" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B343" t="s">
+        <v>664</v>
+      </c>
+      <c r="C343" t="s">
+        <v>664</v>
+      </c>
+      <c r="D343" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="344" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B344" t="s">
+        <v>568</v>
+      </c>
+      <c r="C344" t="s">
+        <v>568</v>
+      </c>
+      <c r="D344" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="345" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B345" t="s">
+        <v>572</v>
+      </c>
+      <c r="C345" t="s">
+        <v>572</v>
+      </c>
+      <c r="D345" t="s">
+        <v>569</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B347:B1048576 B1 B228:B291">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="B346:B1048576 B1">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D131">
-    <cfRule type="duplicateValues" dxfId="1" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="91"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C228:C291 D2:D227">
-    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+  <conditionalFormatting sqref="B346:B1048576 B1:B227">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C228:C251 D2:D227">
+    <cfRule type="duplicateValues" dxfId="1" priority="203"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B228:B251">
+    <cfRule type="duplicateValues" dxfId="0" priority="205"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
